--- a/backend/nodejs/templates/KPM_Import_Product.xlsx
+++ b/backend/nodejs/templates/KPM_Import_Product.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TP\Desktop\KPM\backend\nodejs\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FFA737-FFCF-43E4-A3ED-1F03DDC3D091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407A64FB-F31E-430C-AD2F-F914B0A5A0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBB0906C-0CA5-40FD-8E8B-61911B6F40BC}"/>
   </bookViews>
@@ -648,6 +648,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -684,6 +685,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -702,16 +712,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1130,35 +1130,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="17" t="e" vm="1">
+      <c r="A1" s="18" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:19" ht="31.8" thickBot="1">
-      <c r="A2" s="18"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="26"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="28.8" customHeight="1" thickBot="1">
-      <c r="A3" s="19"/>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
     </row>
     <row r="4" spans="1:19" ht="23.4">
       <c r="A4" s="14" t="s">
@@ -1187,9 +1187,9 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="16.8">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
@@ -1201,9 +1201,9 @@
       <c r="S5" s="3"/>
     </row>
     <row r="6" spans="1:19" ht="16.8">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
@@ -1215,9 +1215,9 @@
       <c r="S6" s="3"/>
     </row>
     <row r="7" spans="1:19" ht="16.8">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
@@ -1226,9 +1226,9 @@
       <c r="Q7" s="3"/>
     </row>
     <row r="8" spans="1:19" ht="18">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
@@ -1238,9 +1238,9 @@
       <c r="S8" s="4"/>
     </row>
     <row r="9" spans="1:19" ht="18">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
@@ -1251,9 +1251,9 @@
       <c r="S9" s="3"/>
     </row>
     <row r="10" spans="1:19" ht="18">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
@@ -1265,9 +1265,9 @@
       <c r="S10" s="3"/>
     </row>
     <row r="11" spans="1:19" ht="16.8">
-      <c r="A11" s="38"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
@@ -1956,10 +1956,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.6">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -1970,14 +1970,14 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.8">
-      <c r="A3" s="36"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
     </row>
     <row r="4" spans="1:4" ht="16.8">
-      <c r="A4" s="36"/>
-      <c r="B4" s="30"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="10" t="s">
         <v>39</v>
       </c>
@@ -1986,52 +1986,52 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.8">
-      <c r="A5" s="36"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A6" s="37"/>
-      <c r="B6" s="31"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="12" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" ht="16.8">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="33" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.8">
-      <c r="A8" s="36"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="35"/>
     </row>
     <row r="10" spans="1:4" ht="16.8">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="9" t="s">
@@ -2042,14 +2042,14 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.8">
-      <c r="A11" s="36"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="12" t="s">
         <v>55</v>
       </c>
@@ -2058,125 +2058,122 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.8">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="33" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16.8">
-      <c r="A14" s="33"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="34"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="34"/>
     </row>
     <row r="15" spans="1:4" ht="16.8">
-      <c r="A15" s="33"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="30"/>
+      <c r="D15" s="34"/>
     </row>
     <row r="16" spans="1:4" ht="16.8">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="34"/>
     </row>
     <row r="17" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="31"/>
+      <c r="D17" s="35"/>
     </row>
     <row r="18" spans="1:4" ht="33.6">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="33" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8">
-      <c r="A19" s="33"/>
-      <c r="B19" s="30"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="11"/>
-      <c r="D19" s="30"/>
+      <c r="D19" s="34"/>
     </row>
     <row r="20" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A20" s="34"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="31"/>
+      <c r="D20" s="35"/>
     </row>
     <row r="21" spans="1:4" ht="16.8">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="33" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8">
-      <c r="A22" s="33"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="11"/>
-      <c r="D22" s="30"/>
+      <c r="D22" s="34"/>
     </row>
     <row r="23" spans="1:4" ht="16.8">
-      <c r="A23" s="33"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="34"/>
     </row>
     <row r="24" spans="1:4" ht="16.8">
-      <c r="A24" s="33"/>
-      <c r="B24" s="30"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
     </row>
     <row r="25" spans="1:4" ht="17.399999999999999" thickBot="1">
-      <c r="A25" s="34"/>
-      <c r="B25" s="31"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="31"/>
+      <c r="D25" s="35"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="16">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
     <mergeCell ref="D21:D25"/>
@@ -2186,8 +2183,11 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="D7:D9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/nodejs/templates/KPM_Import_Product.xlsx
+++ b/backend/nodejs/templates/KPM_Import_Product.xlsx
@@ -8,15 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TP\Desktop\KPM\backend\nodejs\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407A64FB-F31E-430C-AD2F-F914B0A5A0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F4284D-7950-46F8-BD8A-38710056F1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBB0906C-0CA5-40FD-8E8B-61911B6F40BC}"/>
   </bookViews>
   <sheets>
     <sheet name="KPM_Import_Product" sheetId="1" r:id="rId1"/>
     <sheet name="Import rules" sheetId="3" r:id="rId2"/>
-    <sheet name="HiddenData" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="HiddenData" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="Cua">HiddenData!$E$5:$E$9</definedName>
+    <definedName name="CuaSo">HiddenData!$E$10:$E$12</definedName>
+    <definedName name="DanhSachCha">HiddenData!$A$1:$A$5</definedName>
+    <definedName name="data_config">HiddenData!$E$1:$G$18</definedName>
+    <definedName name="DataComponents">HiddenData!$E$1:$F$18</definedName>
+    <definedName name="HangRao">HiddenData!$E$1:$E$4</definedName>
+    <definedName name="MaiNha">HiddenData!$E$13:$E$15</definedName>
+    <definedName name="VatDung">HiddenData!$E$16:$E$18</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -60,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="99">
   <si>
     <t>Mã sản phẩm (*)</t>
   </si>
@@ -77,88 +87,16 @@
     <t>Link ảnh chính</t>
   </si>
   <si>
-    <t>Link ảnh phụ (Cách nhau bằng dấu phẩy)</t>
-  </si>
-  <si>
     <t>Cổng sắt CNC 4 cánh họa tiết Trống Đồng</t>
   </si>
   <si>
     <t>CS-TRONGDONG-4C</t>
   </si>
   <si>
-    <t>DM-CUA-C2C</t>
-  </si>
-  <si>
     <t>DM-CUA-C4C</t>
   </si>
   <si>
-    <t>DM-CUA-LUA</t>
-  </si>
-  <si>
-    <t>DM-CUA-KDL</t>
-  </si>
-  <si>
-    <t>DM-CUA-CUON</t>
-  </si>
-  <si>
-    <t>DM-CUA-DI</t>
-  </si>
-  <si>
     <t>DM-HR-CNC</t>
-  </si>
-  <si>
-    <t>DM-HR-SMT</t>
-  </si>
-  <si>
-    <t>DM-HR-CHONG</t>
-  </si>
-  <si>
-    <t>DM-HR-THEP</t>
-  </si>
-  <si>
-    <t>DM-LC-BC</t>
-  </si>
-  <si>
-    <t>DM-LC-CNC</t>
-  </si>
-  <si>
-    <t>DM-CS-MO</t>
-  </si>
-  <si>
-    <t>DM-CS-BV</t>
-  </si>
-  <si>
-    <t>DM-CS-GIENG</t>
-  </si>
-  <si>
-    <t>DM-CT-BO</t>
-  </si>
-  <si>
-    <t>DM-CT-LC</t>
-  </si>
-  <si>
-    <t>DM-NT-BAN</t>
-  </si>
-  <si>
-    <t>DM-NT-GHE</t>
-  </si>
-  <si>
-    <t>DM-NT-GIUONG</t>
-  </si>
-  <si>
-    <t>DM-GD-KE</t>
-  </si>
-  <si>
-    <t>DM-GD-MOC</t>
-  </si>
-  <si>
-    <t>DM-PK-DUC</t>
-  </si>
-  <si>
-    <t>DM-PK-MAI</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
   <si>
     <t>(Cột A) TÊN CỘT</t>
@@ -298,12 +236,198 @@
   <si>
     <t>"Lưu ý: Vui lòng đọc kỹ sheet [Hướng Dẫn Import] trước khi nhập liệu. Các cột có dấu () là bắt buộc nhập."</t>
   </si>
+  <si>
+    <t>Hàng rào sắt hộp</t>
+  </si>
+  <si>
+    <t>Hàng rào CNC</t>
+  </si>
+  <si>
+    <t>Hàng rào chống trộm</t>
+  </si>
+  <si>
+    <t>Hàng rào lưới</t>
+  </si>
+  <si>
+    <t>Cửa sắt</t>
+  </si>
+  <si>
+    <t>Cửa nhôm Xingfa</t>
+  </si>
+  <si>
+    <t>Cửa kéo Đài Loan</t>
+  </si>
+  <si>
+    <t>Cửa cuốn</t>
+  </si>
+  <si>
+    <t>Cửa 1 cánh</t>
+  </si>
+  <si>
+    <t>Cửa sổ 1 cánh</t>
+  </si>
+  <si>
+    <t>Cửa sổ 2 cánh</t>
+  </si>
+  <si>
+    <t>Khung sắt bảo vệ</t>
+  </si>
+  <si>
+    <t>Mái tôn</t>
+  </si>
+  <si>
+    <t>Mái kính</t>
+  </si>
+  <si>
+    <t>Mái vòm</t>
+  </si>
+  <si>
+    <t>Bàn làm việc</t>
+  </si>
+  <si>
+    <t>Ghế sắt</t>
+  </si>
+  <si>
+    <t>Kệ trang trí</t>
+  </si>
+  <si>
+    <t>Tên danh mục</t>
+  </si>
+  <si>
+    <t>Giá phụ thu</t>
+  </si>
+  <si>
+    <t>Cua</t>
+  </si>
+  <si>
+    <t>HangRao</t>
+  </si>
+  <si>
+    <t>CuaSo</t>
+  </si>
+  <si>
+    <t>MaiNha</t>
+  </si>
+  <si>
+    <t>VatDung</t>
+  </si>
+  <si>
+    <t>[{"name":"Thân hàng rào","is_required":true},{"name":"Mũi chông sắt","is_required":false}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung viền bao","is_required":true},{"name":"Tấm thép cắt CNC","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Thân hàng rào","is_required":true},{"name":"Mũi giáo uốn cong","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung cột","is_required":true},{"name":"Lưới thép/B40","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung bao cửa","is_required":true},{"name":"Cánh sắt","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung bao nhôm","is_required":true},{"name":"Cánh nhôm","is_required":true},{"name":"Kính cường lực","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung bao cửa","is_required":true},{"name":"Lá cửa cuốn/kéo","is_required":true},{"name":"Nhíp chéo","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Trục cuốn","is_required":true},{"name":"Nan cửa","is_required":true},{"name":"Hộp che kỹ thuật","is_required":false}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung bao cửa","is_required":true},{"name":"Cánh cửa","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung bao cửa sổ","is_required":true},{"name":"Cánh cửa sổ","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung bao cửa sổ","is_required":true},{"name":"Cánh cửa trái","is_required":true},{"name":"Cánh cửa phải","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung bảo vệ chống trộm","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung sườn chịu lực","is_required":true},{"name":"Tấm lợp tôn","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung sườn đỡ kính","is_required":true},{"name":"Kính cường lực lấy sáng","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung sườn uốn vòm","is_required":true},{"name":"Tấm lợp (Poly/Tôn)","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung chân bàn","is_required":true},{"name":"Mặt bàn","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung chân ghế","is_required":true},{"name":"Mặt ngồi","is_required":true}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Khung kệ đỡ","is_required":true},{"name":"Mặt đợt (Tầng)","is_required":true}]</t>
+  </si>
+  <si>
+    <t>Thành phần cấu tạo</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "phu_kien": "", "loai_son": ""}</t>
+  </si>
+  <si>
+    <t>{"he_nhom": "", "do_day": "", "kinh": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "do_day": "", "phuong_phap": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "do_day": "", "loai_son": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "kieu_dang": "", "bao_hanh": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "loai_luoi": "", "xu_ly_be_mat": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "co_che": "", "thuong_hieu": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "co_che": "", "cong_nghe": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "ung_dung": "", "bao_hanh": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "kieu_mo": "", "do_day": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "kieu_mo": "", "kinh": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "kieu_dang": "", "chong_trom": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "do_day": "", "chong_nong": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "kinh": "", "lay_sang": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "tam_lop": "", "do_ben": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "chieu_cao": "", "phong_cach": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "chịu_luc": "", "ung_dung": ""}</t>
+  </si>
+  <si>
+    <t>{"vat_lieu": "", "phu_kien": "", "chịu_luc": ""}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,6 +529,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -420,7 +551,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -481,105 +612,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -594,11 +626,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -642,13 +683,21 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -658,31 +707,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1123,42 +1157,53 @@
     <col min="2" max="2" width="46.88671875" customWidth="1"/>
     <col min="3" max="3" width="41.109375" customWidth="1"/>
     <col min="4" max="4" width="54.44140625" customWidth="1"/>
-    <col min="5" max="5" width="45.5546875" customWidth="1"/>
-    <col min="6" max="6" width="78.33203125" customWidth="1"/>
-    <col min="7" max="7" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="100.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="91.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" customWidth="1"/>
+    <col min="8" max="8" width="32.44140625" customWidth="1"/>
+    <col min="9" max="9" width="33.77734375" customWidth="1"/>
     <col min="12" max="12" width="35.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="18" t="e" vm="1">
+    <row r="1" spans="1:19" ht="14.4" customHeight="1">
+      <c r="A1" s="22" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23"/>
-    </row>
-    <row r="2" spans="1:19" ht="31.8" thickBot="1">
-      <c r="A2" s="19"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="B1" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:19" ht="31.2">
+      <c r="A2" s="23"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
       <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="28.8" customHeight="1" thickBot="1">
-      <c r="A3" s="20"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="27" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="1:19" ht="23.4">
       <c r="A4" s="14" t="s">
@@ -1171,13 +1216,22 @@
         <v>2</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="F4" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>5</v>
+      <c r="I4" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="L4" s="2"/>
       <c r="N4" s="2"/>
@@ -1190,9 +1244,15 @@
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="15"/>
+      <c r="G5" s="15" t="str">
+        <f>IF(AND(NOT(ISBLANK(A5)), NOT(ISBLANK(B5))), 1000000, "")</f>
+        <v/>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="20"/>
       <c r="L5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -1204,9 +1264,15 @@
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15" t="str">
+        <f t="shared" ref="G6:G69" si="0">IF(AND(NOT(ISBLANK(A6)), NOT(ISBLANK(B6))), 1000000, "")</f>
+        <v/>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
       <c r="L6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1218,9 +1284,15 @@
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
       <c r="L7" s="3"/>
       <c r="N7" s="3"/>
       <c r="Q7" s="3"/>
@@ -1229,9 +1301,15 @@
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
       <c r="L8" s="3"/>
       <c r="O8" s="4"/>
       <c r="R8" s="4"/>
@@ -1241,9 +1319,15 @@
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
       <c r="N9" s="4"/>
       <c r="O9" s="3"/>
       <c r="Q9" s="4"/>
@@ -1254,9 +1338,15 @@
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
       <c r="L10" s="4"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1268,9 +1358,15 @@
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
       <c r="L11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1278,655 +1374,1362 @@
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="1:19" ht="18">
-      <c r="A12" s="16"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
       <c r="L12" s="3"/>
       <c r="O12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="4"/>
     </row>
     <row r="13" spans="1:19" ht="18">
-      <c r="A13" s="16"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
       <c r="L13" s="3"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="3"/>
       <c r="S13" s="4"/>
     </row>
     <row r="14" spans="1:19" ht="18">
-      <c r="A14" s="16"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
       <c r="O14" s="4"/>
       <c r="Q14" s="5"/>
       <c r="R14" s="3"/>
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19" ht="16.8">
-      <c r="A15" s="16"/>
+      <c r="A15" s="21"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
       <c r="O15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="7"/>
     </row>
     <row r="16" spans="1:19" ht="18">
-      <c r="A16" s="16"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" t="s">
-        <v>32</v>
-      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
       <c r="O16" s="3"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:19" ht="18">
-      <c r="A17" s="16"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
       <c r="O17" s="3"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="3"/>
       <c r="S17" s="4"/>
     </row>
     <row r="18" spans="1:19" ht="16.8">
-      <c r="A18" s="16"/>
+      <c r="A18" s="21"/>
       <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
       <c r="O18" s="3"/>
       <c r="Q18" s="7"/>
       <c r="S18" s="3"/>
     </row>
     <row r="19" spans="1:19" ht="18">
-      <c r="A19" s="16"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
       <c r="R19" s="4"/>
       <c r="S19" s="3"/>
     </row>
     <row r="20" spans="1:19" ht="18">
-      <c r="A20" s="16"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
+      <c r="C20" s="21"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
       <c r="O20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
     <row r="21" spans="1:19" ht="16.8">
-      <c r="A21" s="16"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
       <c r="O21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:19" ht="16.8">
-      <c r="A22" s="16"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
       <c r="O22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:19" ht="16.8">
-      <c r="A23" s="16"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
       <c r="O23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="6"/>
     </row>
     <row r="24" spans="1:19" ht="16.8">
-      <c r="A24" s="16"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
       <c r="O24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="1:19" ht="16.8">
-      <c r="A25" s="16"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
     </row>
     <row r="26" spans="1:19" ht="16.8">
-      <c r="A26" s="16"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
     </row>
     <row r="27" spans="1:19" ht="16.8">
-      <c r="A27" s="16"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
     </row>
     <row r="28" spans="1:19" ht="16.8">
-      <c r="A28" s="16"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
     </row>
     <row r="29" spans="1:19" ht="16.8">
-      <c r="A29" s="16"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
     </row>
     <row r="30" spans="1:19" ht="16.8">
-      <c r="A30" s="16"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
     </row>
     <row r="31" spans="1:19" ht="16.8">
-      <c r="A31" s="16"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:19" ht="16.8">
-      <c r="A32" s="16"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-    </row>
-    <row r="33" spans="1:6" ht="16.8">
-      <c r="A33" s="16"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33" spans="1:9" ht="16.8">
+      <c r="A33" s="21"/>
       <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-    </row>
-    <row r="34" spans="1:6" ht="16.8">
-      <c r="A34" s="16"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15" t="str">
+        <f>IF(AND(NOT(ISBLANK(A33)), NOT(ISBLANK(B33))), 1000000, "")</f>
+        <v/>
+      </c>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+    </row>
+    <row r="34" spans="1:9" ht="16.8">
+      <c r="A34" s="21"/>
       <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-    </row>
-    <row r="35" spans="1:6" ht="16.8">
-      <c r="A35" s="16"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15" t="str">
+        <f>IF(AND(NOT(ISBLANK(A34)), NOT(ISBLANK(B34))), 1000000, "")</f>
+        <v/>
+      </c>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+    </row>
+    <row r="35" spans="1:9" ht="16.8">
+      <c r="A35" s="21"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-    </row>
-    <row r="36" spans="1:6" ht="16.8">
-      <c r="A36" s="16"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+    </row>
+    <row r="36" spans="1:9" ht="16.8">
+      <c r="A36" s="21"/>
       <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-    </row>
-    <row r="37" spans="1:6" ht="16.8">
-      <c r="A37" s="16"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15" t="str">
+        <f>IF(AND(NOT(ISBLANK(A36)), NOT(ISBLANK(B36))), 1000000, "")</f>
+        <v/>
+      </c>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+    </row>
+    <row r="37" spans="1:9" ht="16.8">
+      <c r="A37" s="21"/>
       <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-    </row>
-    <row r="38" spans="1:6" ht="16.8">
-      <c r="A38" s="16"/>
+      <c r="C37" s="21"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15" t="str">
+        <f>IF(AND(NOT(ISBLANK(A37)), NOT(ISBLANK(B37))), 1000000, "")</f>
+        <v/>
+      </c>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+    </row>
+    <row r="38" spans="1:9" ht="16.8">
+      <c r="A38" s="21"/>
       <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-    </row>
-    <row r="39" spans="1:6" ht="16.8">
+      <c r="C38" s="21"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+    </row>
+    <row r="39" spans="1:9" ht="16.8">
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-    </row>
-    <row r="40" spans="1:6" ht="16.8">
+      <c r="D39" s="20"/>
+      <c r="E39" s="20" t="str">
+        <f>IF(ISBLANK(D39), "", VLOOKUP(D39, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F39" s="15" t="str">
+        <f>IF(ISBLANK(D39), "", VLOOKUP(D39, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G39" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:9" ht="16.8">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-    </row>
-    <row r="41" spans="1:6" ht="16.8">
+      <c r="D40" s="20"/>
+      <c r="E40" s="20" t="str">
+        <f>IF(ISBLANK(D40), "", VLOOKUP(D40, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F40" s="15" t="str">
+        <f>IF(ISBLANK(D40), "", VLOOKUP(D40, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G40" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.8">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-    </row>
-    <row r="42" spans="1:6" ht="16.8">
+      <c r="D41" s="20"/>
+      <c r="E41" s="20" t="str">
+        <f>IF(ISBLANK(D41), "", VLOOKUP(D41, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F41" s="15" t="str">
+        <f>IF(ISBLANK(D41), "", VLOOKUP(D41, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G41" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:9" ht="16.8">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-    </row>
-    <row r="43" spans="1:6" ht="16.8">
+      <c r="D42" s="20"/>
+      <c r="E42" s="20" t="str">
+        <f>IF(ISBLANK(D42), "", VLOOKUP(D42, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F42" s="15" t="str">
+        <f>IF(ISBLANK(D42), "", VLOOKUP(D42, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G42" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:9" ht="16.8">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" ht="16.8">
+      <c r="D43" s="20"/>
+      <c r="E43" s="20" t="str">
+        <f>IF(ISBLANK(D43), "", VLOOKUP(D43, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F43" s="15" t="str">
+        <f>IF(ISBLANK(D43), "", VLOOKUP(D43, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G43" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:9" ht="16.8">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-    </row>
-    <row r="45" spans="1:6" ht="16.8">
+      <c r="D44" s="20"/>
+      <c r="E44" s="20" t="str">
+        <f>IF(ISBLANK(D44), "", VLOOKUP(D44, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F44" s="15" t="str">
+        <f>IF(ISBLANK(D44), "", VLOOKUP(D44, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G44" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+    </row>
+    <row r="45" spans="1:9" ht="16.8">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-    </row>
-    <row r="46" spans="1:6" ht="16.8">
+      <c r="D45" s="20"/>
+      <c r="E45" s="20" t="str">
+        <f>IF(ISBLANK(D45), "", VLOOKUP(D45, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F45" s="15" t="str">
+        <f>IF(ISBLANK(D45), "", VLOOKUP(D45, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G45" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+    </row>
+    <row r="46" spans="1:9" ht="16.8">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-    </row>
-    <row r="47" spans="1:6" ht="16.8">
+      <c r="D46" s="20"/>
+      <c r="E46" s="20" t="str">
+        <f>IF(ISBLANK(D46), "", VLOOKUP(D46, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F46" s="15" t="str">
+        <f>IF(ISBLANK(D46), "", VLOOKUP(D46, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G46" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:9" ht="16.8">
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-    </row>
-    <row r="48" spans="1:6" ht="16.8">
+      <c r="D47" s="20"/>
+      <c r="E47" s="20" t="str">
+        <f>IF(ISBLANK(D47), "", VLOOKUP(D47, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F47" s="15" t="str">
+        <f>IF(ISBLANK(D47), "", VLOOKUP(D47, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G47" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+    </row>
+    <row r="48" spans="1:9" ht="16.8">
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-    </row>
-    <row r="49" spans="1:6" ht="16.8">
+      <c r="D48" s="20"/>
+      <c r="E48" s="20" t="str">
+        <f>IF(ISBLANK(D48), "", VLOOKUP(D48, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F48" s="15" t="str">
+        <f>IF(ISBLANK(D48), "", VLOOKUP(D48, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G48" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+    </row>
+    <row r="49" spans="1:9" ht="16.8">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-    </row>
-    <row r="50" spans="1:6" ht="16.8">
+      <c r="D49" s="20"/>
+      <c r="E49" s="20" t="str">
+        <f>IF(ISBLANK(D49), "", VLOOKUP(D49, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F49" s="15" t="str">
+        <f>IF(ISBLANK(D49), "", VLOOKUP(D49, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G49" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+    </row>
+    <row r="50" spans="1:9" ht="16.8">
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-    </row>
-    <row r="51" spans="1:6" ht="16.8">
+      <c r="D50" s="20"/>
+      <c r="E50" s="20" t="str">
+        <f>IF(ISBLANK(D50), "", VLOOKUP(D50, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F50" s="15" t="str">
+        <f>IF(ISBLANK(D50), "", VLOOKUP(D50, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G50" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+    </row>
+    <row r="51" spans="1:9" ht="16.8">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-    </row>
-    <row r="52" spans="1:6" ht="16.8">
+      <c r="D51" s="20"/>
+      <c r="E51" s="20" t="str">
+        <f>IF(ISBLANK(D51), "", VLOOKUP(D51, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F51" s="15" t="str">
+        <f>IF(ISBLANK(D51), "", VLOOKUP(D51, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G51" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+    </row>
+    <row r="52" spans="1:9" ht="16.8">
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-    </row>
-    <row r="53" spans="1:6" ht="16.8">
+      <c r="D52" s="20"/>
+      <c r="E52" s="20" t="str">
+        <f>IF(ISBLANK(D52), "", VLOOKUP(D52, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F52" s="15" t="str">
+        <f>IF(ISBLANK(D52), "", VLOOKUP(D52, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G52" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+    </row>
+    <row r="53" spans="1:9" ht="16.8">
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-    </row>
-    <row r="54" spans="1:6" ht="16.8">
+      <c r="D53" s="20"/>
+      <c r="E53" s="20" t="str">
+        <f>IF(ISBLANK(D53), "", VLOOKUP(D53, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F53" s="15" t="str">
+        <f>IF(ISBLANK(D53), "", VLOOKUP(D53, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G53" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+    </row>
+    <row r="54" spans="1:9" ht="16.8">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-    </row>
-    <row r="55" spans="1:6" ht="16.8">
+      <c r="D54" s="20"/>
+      <c r="E54" s="20" t="str">
+        <f>IF(ISBLANK(D54), "", VLOOKUP(D54, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F54" s="15" t="str">
+        <f>IF(ISBLANK(D54), "", VLOOKUP(D54, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G54" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+    </row>
+    <row r="55" spans="1:9" ht="16.8">
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-    </row>
-    <row r="56" spans="1:6" ht="16.8">
+      <c r="D55" s="20"/>
+      <c r="E55" s="20" t="str">
+        <f>IF(ISBLANK(D55), "", VLOOKUP(D55, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F55" s="15" t="str">
+        <f>IF(ISBLANK(D55), "", VLOOKUP(D55, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G55" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+    </row>
+    <row r="56" spans="1:9" ht="16.8">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-    </row>
-    <row r="57" spans="1:6" ht="16.8">
+      <c r="D56" s="20"/>
+      <c r="E56" s="20" t="str">
+        <f>IF(ISBLANK(D56), "", VLOOKUP(D56, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F56" s="15" t="str">
+        <f>IF(ISBLANK(D56), "", VLOOKUP(D56, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G56" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+    </row>
+    <row r="57" spans="1:9" ht="16.8">
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-    </row>
-    <row r="58" spans="1:6" ht="16.8">
+      <c r="D57" s="20"/>
+      <c r="E57" s="20" t="str">
+        <f>IF(ISBLANK(D57), "", VLOOKUP(D57, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F57" s="15" t="str">
+        <f>IF(ISBLANK(D57), "", VLOOKUP(D57, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G57" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+    </row>
+    <row r="58" spans="1:9" ht="16.8">
       <c r="A58" s="16"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-    </row>
-    <row r="59" spans="1:6" ht="16.8">
+      <c r="D58" s="20"/>
+      <c r="E58" s="20" t="str">
+        <f>IF(ISBLANK(D58), "", VLOOKUP(D58, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F58" s="15" t="str">
+        <f>IF(ISBLANK(D58), "", VLOOKUP(D58, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G58" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+    </row>
+    <row r="59" spans="1:9" ht="16.8">
       <c r="A59" s="16"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-    </row>
-    <row r="60" spans="1:6" ht="16.8">
+      <c r="D59" s="20"/>
+      <c r="E59" s="20" t="str">
+        <f>IF(ISBLANK(D59), "", VLOOKUP(D59, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F59" s="15" t="str">
+        <f>IF(ISBLANK(D59), "", VLOOKUP(D59, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G59" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+    </row>
+    <row r="60" spans="1:9" ht="16.8">
       <c r="A60" s="16"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-    </row>
-    <row r="61" spans="1:6" ht="16.8">
+      <c r="D60" s="20"/>
+      <c r="E60" s="20" t="str">
+        <f>IF(ISBLANK(D60), "", VLOOKUP(D60, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F60" s="15" t="str">
+        <f>IF(ISBLANK(D60), "", VLOOKUP(D60, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G60" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+    </row>
+    <row r="61" spans="1:9" ht="16.8">
       <c r="A61" s="16"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-    </row>
-    <row r="62" spans="1:6" ht="16.8">
+      <c r="D61" s="20"/>
+      <c r="E61" s="20" t="str">
+        <f>IF(ISBLANK(D61), "", VLOOKUP(D61, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F61" s="15" t="str">
+        <f>IF(ISBLANK(D61), "", VLOOKUP(D61, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G61" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+    </row>
+    <row r="62" spans="1:9" ht="16.8">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-    </row>
-    <row r="63" spans="1:6" ht="16.8">
+      <c r="D62" s="20"/>
+      <c r="E62" s="20" t="str">
+        <f>IF(ISBLANK(D62), "", VLOOKUP(D62, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F62" s="15" t="str">
+        <f>IF(ISBLANK(D62), "", VLOOKUP(D62, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G62" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+    </row>
+    <row r="63" spans="1:9" ht="16.8">
       <c r="A63" s="16"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-    </row>
-    <row r="64" spans="1:6" ht="16.8">
+      <c r="D63" s="20"/>
+      <c r="E63" s="20" t="str">
+        <f>IF(ISBLANK(D63), "", VLOOKUP(D63, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F63" s="15" t="str">
+        <f>IF(ISBLANK(D63), "", VLOOKUP(D63, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G63" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" ht="16.8">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-    </row>
-    <row r="65" spans="1:6" ht="16.8">
+      <c r="D64" s="20"/>
+      <c r="E64" s="20" t="str">
+        <f>IF(ISBLANK(D64), "", VLOOKUP(D64, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F64" s="15" t="str">
+        <f>IF(ISBLANK(D64), "", VLOOKUP(D64, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G64" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+    </row>
+    <row r="65" spans="1:9" ht="16.8">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-    </row>
-    <row r="66" spans="1:6" ht="16.8">
+      <c r="D65" s="20"/>
+      <c r="E65" s="20" t="str">
+        <f>IF(ISBLANK(D65), "", VLOOKUP(D65, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F65" s="15" t="str">
+        <f>IF(ISBLANK(D65), "", VLOOKUP(D65, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G65" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" ht="16.8">
       <c r="A66" s="16"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-    </row>
-    <row r="67" spans="1:6" ht="16.8">
+      <c r="D66" s="20"/>
+      <c r="E66" s="20" t="str">
+        <f>IF(ISBLANK(D66), "", VLOOKUP(D66, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F66" s="15" t="str">
+        <f>IF(ISBLANK(D66), "", VLOOKUP(D66, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G66" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" ht="16.8">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-    </row>
-    <row r="68" spans="1:6" ht="16.8">
+      <c r="D67" s="20"/>
+      <c r="E67" s="20" t="str">
+        <f>IF(ISBLANK(D67), "", VLOOKUP(D67, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F67" s="15" t="str">
+        <f>IF(ISBLANK(D67), "", VLOOKUP(D67, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G67" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+    </row>
+    <row r="68" spans="1:9" ht="16.8">
       <c r="A68" s="16"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-    </row>
-    <row r="69" spans="1:6" ht="16.8">
+      <c r="D68" s="20"/>
+      <c r="E68" s="20" t="str">
+        <f>IF(ISBLANK(D68), "", VLOOKUP(D68, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F68" s="15" t="str">
+        <f>IF(ISBLANK(D68), "", VLOOKUP(D68, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G68" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+    </row>
+    <row r="69" spans="1:9" ht="16.8">
       <c r="A69" s="16"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-    </row>
-    <row r="70" spans="1:6" ht="16.8">
+      <c r="D69" s="20"/>
+      <c r="E69" s="20" t="str">
+        <f>IF(ISBLANK(D69), "", VLOOKUP(D69, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F69" s="15" t="str">
+        <f>IF(ISBLANK(D69), "", VLOOKUP(D69, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G69" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" ht="16.8">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-    </row>
-    <row r="71" spans="1:6" ht="16.8">
+      <c r="D70" s="20"/>
+      <c r="E70" s="20" t="str">
+        <f>IF(ISBLANK(D70), "", VLOOKUP(D70, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F70" s="15" t="str">
+        <f>IF(ISBLANK(D70), "", VLOOKUP(D70, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G70" s="15" t="str">
+        <f t="shared" ref="G70:G84" si="1">IF(AND(NOT(ISBLANK(A70)), NOT(ISBLANK(B70))), 1000000, "")</f>
+        <v/>
+      </c>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+    </row>
+    <row r="71" spans="1:9" ht="16.8">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-    </row>
-    <row r="72" spans="1:6" ht="16.8">
+      <c r="D71" s="20"/>
+      <c r="E71" s="20" t="str">
+        <f>IF(ISBLANK(D71), "", VLOOKUP(D71, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F71" s="15" t="str">
+        <f>IF(ISBLANK(D71), "", VLOOKUP(D71, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G71" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" ht="16.8">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-    </row>
-    <row r="73" spans="1:6" ht="16.8">
+      <c r="D72" s="20"/>
+      <c r="E72" s="20" t="str">
+        <f>IF(ISBLANK(D72), "", VLOOKUP(D72, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F72" s="15" t="str">
+        <f>IF(ISBLANK(D72), "", VLOOKUP(D72, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G72" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9" ht="16.8">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-    </row>
-    <row r="74" spans="1:6" ht="16.8">
+      <c r="D73" s="20"/>
+      <c r="E73" s="20" t="str">
+        <f>IF(ISBLANK(D73), "", VLOOKUP(D73, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F73" s="15" t="str">
+        <f>IF(ISBLANK(D73), "", VLOOKUP(D73, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G73" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+    </row>
+    <row r="74" spans="1:9" ht="16.8">
       <c r="A74" s="16"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-    </row>
-    <row r="75" spans="1:6" ht="16.8">
+      <c r="D74" s="20"/>
+      <c r="E74" s="20" t="str">
+        <f>IF(ISBLANK(D74), "", VLOOKUP(D74, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F74" s="15" t="str">
+        <f>IF(ISBLANK(D74), "", VLOOKUP(D74, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G74" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+    </row>
+    <row r="75" spans="1:9" ht="16.8">
       <c r="A75" s="16"/>
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-    </row>
-    <row r="76" spans="1:6" ht="16.8">
+      <c r="D75" s="20"/>
+      <c r="E75" s="20" t="str">
+        <f>IF(ISBLANK(D75), "", VLOOKUP(D75, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F75" s="15" t="str">
+        <f>IF(ISBLANK(D75), "", VLOOKUP(D75, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G75" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+    </row>
+    <row r="76" spans="1:9" ht="16.8">
       <c r="A76" s="16"/>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-    </row>
-    <row r="77" spans="1:6" ht="16.8">
+      <c r="D76" s="20"/>
+      <c r="E76" s="20" t="str">
+        <f>IF(ISBLANK(D76), "", VLOOKUP(D76, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F76" s="15" t="str">
+        <f>IF(ISBLANK(D76), "", VLOOKUP(D76, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G76" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+    </row>
+    <row r="77" spans="1:9" ht="16.8">
       <c r="A77" s="16"/>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-    </row>
-    <row r="78" spans="1:6" ht="16.8">
+      <c r="D77" s="20"/>
+      <c r="E77" s="20" t="str">
+        <f>IF(ISBLANK(D77), "", VLOOKUP(D77, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F77" s="15" t="str">
+        <f>IF(ISBLANK(D77), "", VLOOKUP(D77, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G77" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+    </row>
+    <row r="78" spans="1:9" ht="16.8">
       <c r="A78" s="16"/>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-    </row>
-    <row r="79" spans="1:6" ht="16.8">
+      <c r="D78" s="20"/>
+      <c r="E78" s="20" t="str">
+        <f>IF(ISBLANK(D78), "", VLOOKUP(D78, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F78" s="15" t="str">
+        <f>IF(ISBLANK(D78), "", VLOOKUP(D78, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G78" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+    </row>
+    <row r="79" spans="1:9" ht="16.8">
       <c r="A79" s="16"/>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-    </row>
-    <row r="80" spans="1:6" ht="16.8">
+      <c r="D79" s="20"/>
+      <c r="E79" s="20" t="str">
+        <f>IF(ISBLANK(D79), "", VLOOKUP(D79, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F79" s="15" t="str">
+        <f>IF(ISBLANK(D79), "", VLOOKUP(D79, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G79" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+    </row>
+    <row r="80" spans="1:9" ht="16.8">
       <c r="A80" s="16"/>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-    </row>
-    <row r="81" spans="1:6" ht="16.8">
+      <c r="D80" s="20"/>
+      <c r="E80" s="20" t="str">
+        <f>IF(ISBLANK(D80), "", VLOOKUP(D80, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F80" s="15" t="str">
+        <f>IF(ISBLANK(D80), "", VLOOKUP(D80, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G80" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+    </row>
+    <row r="81" spans="1:9" ht="16.8">
       <c r="A81" s="16"/>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-    </row>
-    <row r="82" spans="1:6" ht="16.8">
+      <c r="D81" s="20"/>
+      <c r="E81" s="20" t="str">
+        <f>IF(ISBLANK(D81), "", VLOOKUP(D81, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F81" s="15" t="str">
+        <f>IF(ISBLANK(D81), "", VLOOKUP(D81, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G81" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+    </row>
+    <row r="82" spans="1:9" ht="16.8">
       <c r="A82" s="16"/>
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
-    </row>
-    <row r="83" spans="1:6" ht="16.8">
+      <c r="D82" s="20"/>
+      <c r="E82" s="20" t="str">
+        <f>IF(ISBLANK(D82), "", VLOOKUP(D82, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F82" s="15" t="str">
+        <f>IF(ISBLANK(D82), "", VLOOKUP(D82, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G82" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+    </row>
+    <row r="83" spans="1:9" ht="16.8">
       <c r="A83" s="16"/>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-    </row>
-    <row r="84" spans="1:6" ht="16.8">
+      <c r="D83" s="20"/>
+      <c r="E83" s="20" t="str">
+        <f>IF(ISBLANK(D83), "", VLOOKUP(D83, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F83" s="15" t="str">
+        <f>IF(ISBLANK(D83), "", VLOOKUP(D83, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G83" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+    </row>
+    <row r="84" spans="1:9" ht="16.8">
       <c r="A84" s="16"/>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20" t="str">
+        <f>IF(ISBLANK(D84), "", VLOOKUP(D84, HiddenData!$E$1:$G$100, 3, FALSE))</f>
+        <v/>
+      </c>
+      <c r="F84" s="15" t="str">
+        <f>IF(ISBLANK(D84), "", VLOOKUP(D84, HiddenData!$E$1:$F$100, 2, FALSE))</f>
+        <v/>
+      </c>
+      <c r="G84" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:F2"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B1:I2"/>
+    <mergeCell ref="B3:I3"/>
   </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Lưu ý" prompt="&quot;Vui lòng điền giá trị vào giữa 2 dấu ngoặc kép. Ví dụ: {&quot;vat_lieu&quot;: &quot;Sắt hộp&quot;, &quot;phu_kien&quot;: &quot;Bản lề&quot;, &quot;loai_son&quot;: &quot;Tĩnh điện&quot;}&quot;" sqref="E5:E84" xr:uid="{4B877D47-D01F-412A-AD2A-EE494517EC5F}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C84" xr:uid="{CC69A34B-1977-4176-B267-36CA48768876}">
+      <formula1>DanhSachCha</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D84" xr:uid="{6F6C420F-45A5-4EB5-ACA5-EA1278F75229}">
+      <formula1>INDIRECT(SUBSTITUTE(C5, " ", ""))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{90E8C98E-D5A7-4127-B4A7-22226F9CC74E}">
-          <x14:formula1>
-            <xm:f>HiddenData!$A$1:$A$24</xm:f>
-          </x14:formula1>
-          <xm:sqref>C12:C84</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -1943,231 +2746,231 @@
   <sheetData>
     <row r="1" spans="1:4" ht="48.6" thickBot="1">
       <c r="A1" s="8" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.6">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="33" t="s">
-        <v>37</v>
+      <c r="B2" s="32" t="s">
+        <v>13</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.8">
-      <c r="A3" s="31"/>
-      <c r="B3" s="34"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
     </row>
     <row r="4" spans="1:4" ht="16.8">
-      <c r="A4" s="31"/>
-      <c r="B4" s="34"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="33"/>
       <c r="C4" s="10" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.8">
-      <c r="A5" s="31"/>
-      <c r="B5" s="34"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="35"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="12" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" ht="16.8">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>37</v>
+      <c r="B7" s="32" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.8">
-      <c r="A8" s="31"/>
-      <c r="B8" s="34"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="34"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A9" s="32"/>
-      <c r="B9" s="35"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="35"/>
+        <v>19</v>
+      </c>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:4" ht="16.8">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="33" t="s">
-        <v>37</v>
+      <c r="B10" s="32" t="s">
+        <v>13</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.8">
-      <c r="A11" s="31"/>
-      <c r="B11" s="34"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="35"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="12" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.8">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="33" t="s">
-        <v>44</v>
+      <c r="B13" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>46</v>
+        <v>21</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16.8">
-      <c r="A14" s="37"/>
-      <c r="B14" s="34"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="34"/>
+      <c r="D14" s="33"/>
     </row>
     <row r="15" spans="1:4" ht="16.8">
-      <c r="A15" s="37"/>
-      <c r="B15" s="34"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="34"/>
+        <v>32</v>
+      </c>
+      <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:4" ht="16.8">
-      <c r="A16" s="37"/>
-      <c r="B16" s="34"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="34"/>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A17" s="38"/>
-      <c r="B17" s="35"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="35"/>
+        <v>33</v>
+      </c>
+      <c r="D17" s="34"/>
     </row>
     <row r="18" spans="1:4" ht="33.6">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="33" t="s">
-        <v>44</v>
+      <c r="B18" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>49</v>
+        <v>23</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8">
-      <c r="A19" s="37"/>
-      <c r="B19" s="34"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="11"/>
-      <c r="D19" s="34"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" spans="1:4" ht="34.200000000000003" thickBot="1">
-      <c r="A20" s="38"/>
-      <c r="B20" s="35"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="35"/>
+        <v>24</v>
+      </c>
+      <c r="D20" s="34"/>
     </row>
     <row r="21" spans="1:4" ht="16.8">
-      <c r="A21" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>44</v>
+      <c r="A21" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>53</v>
+        <v>27</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8">
-      <c r="A22" s="37"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="11"/>
-      <c r="D22" s="34"/>
+      <c r="D22" s="33"/>
     </row>
     <row r="23" spans="1:4" ht="16.8">
-      <c r="A23" s="37"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="33"/>
       <c r="C23" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="34"/>
+        <v>34</v>
+      </c>
+      <c r="D23" s="33"/>
     </row>
     <row r="24" spans="1:4" ht="16.8">
-      <c r="A24" s="37"/>
-      <c r="B24" s="34"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="33"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="33"/>
     </row>
     <row r="25" spans="1:4" ht="17.399999999999999" thickBot="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="35"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="35"/>
+        <v>28</v>
+      </c>
+      <c r="D25" s="34"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -2196,127 +2999,226 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDDA294A-4A86-4036-8E12-DD122DCB02E9}">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="79.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:7" ht="39" customHeight="1">
       <c r="A1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>31</v>
+        <v>58</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="29.4" customHeight="1">
+      <c r="A2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="23.4" customHeight="1">
+      <c r="A3" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="24" customHeight="1">
+      <c r="A4" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="24" customHeight="1">
+      <c r="A5" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="23.4" customHeight="1">
+      <c r="E6" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="24" customHeight="1">
+      <c r="E7" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="24" customHeight="1">
+      <c r="E8" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="24" customHeight="1">
+      <c r="E9" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="24" customHeight="1">
+      <c r="E10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="24" customHeight="1">
+      <c r="E11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="24" customHeight="1">
+      <c r="E12" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="24" customHeight="1">
+      <c r="E13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="24" customHeight="1">
+      <c r="E14" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="24" customHeight="1">
+      <c r="E15" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="24" customHeight="1">
+      <c r="E16" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" ht="24.6" customHeight="1">
+      <c r="E17" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" ht="23.4" customHeight="1">
+      <c r="E18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
